--- a/data/export/2026-09-21-operations.xlsx
+++ b/data/export/2026-09-21-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -452,7 +452,7 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
@@ -648,29 +648,29 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站博兴路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -901,26 +901,22 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 16分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -928,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -957,7 +953,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -967,22 +963,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1025,26 +1021,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 35分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1052,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1076,12 +1068,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1091,22 +1083,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1144,27 +1136,31 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1172,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1216,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1265,24 +1265,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1389,24 +1389,24 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±10分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路春雅路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1513,24 +1513,24 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±15分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1607,24 +1607,24 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1637,34 +1637,34 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1713,40 +1713,40 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1761,24 +1761,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+          <t>07:21采样：该车到重点站长岛路台儿庄路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1837,40 +1837,40 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1885,24 +1885,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±14分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1961,40 +1961,40 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2009,24 +2009,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±10分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2050,7 +2050,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2075,50 +2075,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2133,34 +2133,34 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数168分钟估算，约±10分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2209,40 +2209,40 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2257,30 +2257,34 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2294,7 +2298,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2304,17 +2308,17 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2324,41 +2328,45 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2373,30 +2381,34 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2410,7 +2422,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2420,61 +2432,65 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2489,22 +2505,26 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2512,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2526,7 +2546,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2536,33 +2556,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2599,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2585,7 +2609,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2605,34 +2629,34 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数156分钟估算，约±6分钟</t>
+          <t>07:20采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2646,7 +2670,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2661,7 +2685,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2681,30 +2705,30 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2714,7 +2738,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2729,30 +2753,34 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：06:20采样，终点ETA 80分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>07:20采样：该车到重点站沪南路御桥路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2776,17 +2804,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2796,41 +2824,45 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2845,34 +2877,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±13分钟</t>
+          <t>07:20采样：该车到重点站丁香路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2886,7 +2918,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2896,12 +2928,12 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2921,40 +2953,40 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2969,19 +3001,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±15分钟</t>
+          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±15分钟</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2991,12 +3023,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3010,7 +3042,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3025,7 +3057,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3045,40 +3077,40 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3093,34 +3125,30 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±11分钟</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3134,47 +3162,3707 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>173分钟</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>173.0</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>13/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>175分钟</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>14/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>156分钟</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>172分钟</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>172.0</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>12/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>167分钟</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>165分钟</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站关岳路康达路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>164分钟</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>156分钟</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数156分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>6/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数149分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:00采样，终点ETA 61分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>116分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 61分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>06:50</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>114分钟</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站张杨北路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="inlineStr">
+      <c r="Z48" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="AD22" s="2" t="inlineStr">
-        <is>
-          <t>3/4</t>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数99分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-operations.xlsx
+++ b/data/export/2026-09-21-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD52"/>
+  <dimension ref="A1:AD73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -450,7 +450,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,31 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 16分钟</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -924,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -948,12 +952,12 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -973,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1020,31 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 35分钟</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1044,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1068,12 +1076,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1093,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1141,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1260,29 +1268,29 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1292,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1316,12 +1324,12 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1331,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1384,29 +1392,29 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路春雅路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1416,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1440,12 +1448,12 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1455,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1518,21 +1526,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1540,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1564,12 +1568,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1579,22 +1583,22 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1637,24 +1641,24 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路台桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1664,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1693,7 +1697,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1713,12 +1717,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1756,29 +1760,29 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站长岛路台儿庄路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1812,12 +1816,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1837,12 +1841,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1885,24 +1889,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±8分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路台桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1912,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1941,7 +1945,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1961,12 +1965,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2009,24 +2013,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路顾家浜路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2036,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2065,7 +2069,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2085,12 +2089,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2133,24 +2137,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2160,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2189,7 +2193,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2209,12 +2213,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2257,24 +2261,24 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±9分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2284,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2313,7 +2317,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2333,12 +2337,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2381,24 +2385,24 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+          <t>08:11采样：该车到重点站东陆路新金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2408,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2437,7 +2441,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2457,12 +2461,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2475,24 +2479,24 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2505,24 +2509,24 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+          <t>08:11采样：该车到重点站新德西路德川路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2532,7 +2536,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2546,7 +2550,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2561,7 +2565,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2581,40 +2585,40 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2629,24 +2633,24 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2656,7 +2660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2670,7 +2674,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2685,7 +2689,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2695,50 +2699,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2753,24 +2757,24 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路御桥路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±12分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2780,7 +2784,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2794,7 +2798,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2804,12 +2808,12 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2819,50 +2823,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2877,34 +2881,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站丁香路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±10分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±12分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2918,7 +2922,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2928,12 +2932,12 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2953,40 +2957,40 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3001,34 +3005,34 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±15分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3042,7 +3046,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3052,12 +3056,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3067,50 +3071,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3125,22 +3129,26 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3148,7 +3156,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3162,7 +3170,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3172,61 +3180,65 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3259,12 +3271,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3278,7 +3290,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3303,18 +3315,22 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3343,7 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3337,7 +3353,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3357,26 +3373,22 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 37分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3384,7 +3396,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3398,7 +3410,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3408,12 +3420,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3423,22 +3435,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3463,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3461,7 +3473,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3476,39 +3488,39 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>175分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3522,7 +3534,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3532,12 +3544,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3557,12 +3569,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -3575,24 +3587,24 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3605,34 +3617,30 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 46分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3646,7 +3654,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3656,17 +3664,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3676,17 +3684,13 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>156.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3699,24 +3703,24 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3729,34 +3733,30 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>172分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 70分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3780,17 +3780,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3800,17 +3800,13 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>172.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3823,64 +3819,60 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>167分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3888,13 +3880,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
       <c r="T28" s="2" t="inlineStr"/>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq29映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3904,17 +3908,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3924,17 +3928,13 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>167.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3947,24 +3947,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3977,34 +3977,30 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站关岳路康达路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4018,7 +4014,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4028,17 +4024,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4048,17 +4044,13 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr">
-        <is>
-          <t>165.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4071,24 +4063,24 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4101,19 +4093,19 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -4123,12 +4115,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4142,7 +4134,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4177,12 +4169,12 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4187,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4205,7 +4197,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4225,34 +4217,34 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>177分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数156分钟估算，约±8分钟</t>
+          <t>08:10采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4266,7 +4258,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4276,12 +4268,12 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4301,12 +4293,12 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4311,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4329,7 +4321,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4349,30 +4341,34 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>08:01采样：该车到重点站沪南路高科西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4386,7 +4382,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4396,17 +4392,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4416,13 +4412,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>9/26</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4465,34 +4465,34 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±12分钟</t>
+          <t>08:10采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4589,30 +4589,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>181分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>08:10采样：该车到重点站沪南路高科西路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4626,7 +4630,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4636,17 +4640,17 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4656,13 +4660,17 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>15/26</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4683,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4685,7 +4693,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4705,30 +4713,34 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>08:01采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4742,7 +4754,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4752,17 +4764,17 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4772,13 +4784,17 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4807,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4801,7 +4817,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4821,34 +4837,34 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数149分钟估算，约±8分钟</t>
+          <t>08:10采样：该车到重点站白桦路明月路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4862,7 +4878,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4877,7 +4893,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4897,40 +4913,40 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4945,30 +4961,34 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:00采样，终点ETA 61分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4982,7 +5002,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4992,17 +5012,17 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5012,41 +5032,45 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5061,30 +5085,30 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>116分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 61分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5098,7 +5122,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5113,7 +5137,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -5123,7 +5147,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5134,35 +5158,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5177,34 +5201,34 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>183分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数161分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5218,7 +5242,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5253,40 +5277,40 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5301,34 +5325,30 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5342,7 +5362,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5352,17 +5372,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5372,45 +5392,41 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5425,19 +5441,19 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5447,12 +5463,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5466,7 +5482,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5501,40 +5517,40 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5549,34 +5565,34 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±12分钟</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5590,7 +5606,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5600,12 +5616,12 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5625,40 +5641,40 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5673,34 +5689,34 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+          <t>08:10采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5714,7 +5730,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5729,7 +5745,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5749,40 +5765,40 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5797,34 +5813,30 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5838,7 +5850,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5848,17 +5860,17 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5868,45 +5880,41 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5921,34 +5929,30 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5962,7 +5966,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5972,17 +5976,17 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5992,45 +5996,41 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -6045,26 +6045,22 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6072,7 +6068,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6086,7 +6082,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6096,17 +6092,17 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6116,45 +6112,41 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6169,34 +6161,30 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>114分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站张杨北路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6210,7 +6198,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6220,17 +6208,17 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6240,45 +6228,41 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6293,34 +6277,34 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6334,7 +6318,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6344,7 +6328,7 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6369,40 +6353,40 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6417,34 +6401,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±9分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±15分钟</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6458,7 +6442,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6468,7 +6452,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6493,40 +6477,40 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6541,34 +6525,34 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±11分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数147分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6582,7 +6566,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6592,7 +6576,7 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6607,22 +6591,22 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -6635,24 +6619,24 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>07:53</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6665,26 +6649,22 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数99分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:00采样，终点ETA 61分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6692,7 +6672,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6706,7 +6686,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6716,17 +6696,17 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6736,17 +6716,13 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -6764,19 +6740,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6789,19 +6765,19 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 7分钟</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr"/>
@@ -6812,7 +6788,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6826,43 +6802,2643 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>105分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>108分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 17分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>113分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>07:30采样：该车到重点站金高路万安街 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站杨高北路洲海路（外高桥保税区） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站五莲路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站航津路地铁站 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站金杨路金桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站航津路地铁站 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站同港路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
           <t>08:11</t>
         </is>
       </c>
-      <c r="W52" s="2" t="inlineStr">
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
-      <c r="X52" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y52" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Z52" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr"/>
-      <c r="AD52" s="2" t="inlineStr">
-        <is>
-          <t>—/15</t>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数102分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>113分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数113分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-operations.xlsx
+++ b/data/export/2026-09-21-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD73"/>
+  <dimension ref="A1:AD79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1516,27 +1516,31 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 13分钟</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1544,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1568,12 +1572,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1593,7 +1597,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
@@ -1641,26 +1645,22 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路台桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1707,22 +1707,22 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1831,22 +1831,22 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1889,24 +1889,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路台桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±9分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2013,19 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路顾家浜路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2137,24 +2137,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±10分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2261,24 +2261,24 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±8分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2385,19 +2385,19 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站东陆路新金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2514,14 +2514,14 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站新德西路德川路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2633,24 +2633,24 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+          <t>08:21采样：该车到重点站博兴路东陆路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2757,24 +2757,24 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±12分钟</t>
+          <t>08:21采样：该车到重点站新川路华东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
@@ -3337,28 +3337,28 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3373,30 +3373,34 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 37分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3410,7 +3414,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3420,12 +3424,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3445,40 +3449,40 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3488,29 +3492,29 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3520,7 +3524,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3534,7 +3538,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3544,12 +3548,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3559,22 +3563,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3587,24 +3591,24 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:26</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3612,27 +3616,31 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 46分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3640,7 +3648,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3654,7 +3662,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3664,33 +3672,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -3703,24 +3715,24 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3728,27 +3740,31 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 70分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3756,7 +3772,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3770,7 +3786,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3780,33 +3796,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3839,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3829,7 +3849,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3839,32 +3859,36 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3872,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3880,25 +3904,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>丁香路锦绣路</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>07:41</t>
-        </is>
-      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr"/>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq29映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3908,17 +3920,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3928,13 +3940,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -3947,24 +3963,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3977,30 +3993,30 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 58分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4014,7 +4030,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4029,7 +4045,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -4039,18 +4055,22 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -4063,56 +4083,52 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4120,7 +4136,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4128,13 +4144,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq29映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4144,17 +4172,17 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4164,17 +4192,13 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>165.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4211,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4197,7 +4221,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4217,34 +4241,30 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>177分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4258,7 +4278,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4268,17 +4288,17 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4288,17 +4308,13 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>177.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4327,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4321,7 +4337,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4341,34 +4357,34 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>162分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站沪南路高科西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±11分钟</t>
+          <t>08:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4382,7 +4398,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4392,7 +4408,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4417,12 +4433,12 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>15/26</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4451,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4445,7 +4461,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4465,34 +4481,34 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>180分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±8分钟</t>
+          <t>08:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4506,7 +4522,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4516,7 +4532,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4541,12 +4557,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4575,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4569,7 +4585,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4589,34 +4605,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>181分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站沪南路高科西路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±13分钟</t>
+          <t>08:20采样：该车到重点站迎春路金松路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4630,7 +4646,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4640,7 +4656,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4665,12 +4681,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>15/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -4683,24 +4699,24 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4713,34 +4729,34 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
+          <t>08:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4754,7 +4770,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4789,12 +4805,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -4807,24 +4823,24 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4837,34 +4853,34 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>181分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站白桦路明月路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站迎春路金松路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4878,7 +4894,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4913,12 +4929,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>17/26</t>
         </is>
       </c>
     </row>
@@ -4931,24 +4947,24 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4966,29 +4982,29 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±9分钟</t>
+          <t>08:01采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5002,7 +5018,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5037,12 +5053,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -5055,24 +5071,24 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5085,30 +5101,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站丁香路锦绣路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5122,7 +5142,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5132,17 +5152,17 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5152,13 +5172,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -5171,24 +5195,24 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5201,34 +5225,34 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>183分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数161分钟，约±6分钟</t>
+          <t>08:20采样：该车到重点站丁香路锦绣路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5242,7 +5266,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5252,7 +5276,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5277,12 +5301,12 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5319,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5305,7 +5329,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5343,7 +5367,7 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5362,7 +5386,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5411,24 +5435,24 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5441,34 +5465,34 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>183分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数161分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5482,7 +5506,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5517,12 +5541,12 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -5535,24 +5559,24 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5565,34 +5589,30 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5616,17 +5636,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5636,17 +5656,13 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5675,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5669,7 +5685,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5689,19 +5705,19 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5711,12 +5727,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5730,7 +5746,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5765,12 +5781,12 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -5783,24 +5799,24 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5813,30 +5829,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5850,7 +5870,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5860,17 +5880,17 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5880,13 +5900,17 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5923,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5909,7 +5933,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5929,30 +5953,34 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5966,7 +5994,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5976,17 +6004,17 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5996,13 +6024,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -6015,7 +6047,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -6025,7 +6057,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6063,7 +6095,7 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6082,7 +6114,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6131,7 +6163,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6141,7 +6173,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6184,7 +6216,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6198,7 +6230,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6247,7 +6279,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6257,7 +6289,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6277,34 +6309,30 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6318,7 +6346,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6328,17 +6356,17 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6348,17 +6376,13 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>166.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6371,24 +6395,24 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6401,34 +6425,30 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±15分钟</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6442,7 +6462,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6452,17 +6472,17 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6472,17 +6492,13 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6495,24 +6511,24 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6525,24 +6541,24 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数147分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -6552,7 +6568,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6566,7 +6582,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6591,50 +6607,50 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6649,30 +6665,34 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:00采样，终点ETA 61分钟</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6686,7 +6706,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6696,17 +6716,17 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6716,41 +6736,45 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6765,30 +6789,34 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 7分钟</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数147分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6802,7 +6830,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6817,7 +6845,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6832,45 +6860,45 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6880,39 +6908,39 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6926,7 +6954,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6936,12 +6964,12 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6961,40 +6989,40 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -7004,39 +7032,39 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7050,22 +7078,22 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>计划发车</t>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -7080,17 +7108,17 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7131,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -7113,7 +7141,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -7133,34 +7161,30 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:00采样，终点ETA 61分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7174,7 +7198,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7184,17 +7208,17 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7204,17 +7228,13 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -7227,24 +7247,24 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7252,39 +7272,35 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7298,7 +7314,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7308,12 +7324,12 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7333,12 +7349,12 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7367,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7361,7 +7377,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7376,27 +7392,31 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 17分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7404,7 +7424,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7418,7 +7438,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7428,12 +7448,12 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7453,12 +7473,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7491,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7481,7 +7501,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7496,24 +7516,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>07:30采样：该车到重点站金高路万安街 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7523,12 +7543,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7542,7 +7562,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7552,12 +7572,12 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7567,22 +7587,22 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7615,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7605,7 +7625,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7625,19 +7645,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>同车下一次反向发车08:45，减去该车自身同类时段历史终点停站中位数17分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7647,12 +7667,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7666,7 +7686,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7681,7 +7701,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7691,22 +7711,22 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7719,7 +7739,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7729,7 +7749,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7744,39 +7764,39 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站杨高北路洲海路（外高桥保税区） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7790,7 +7810,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7800,12 +7820,12 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7815,22 +7835,22 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7843,24 +7863,24 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7868,39 +7888,39 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7914,7 +7934,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7924,12 +7944,12 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7939,22 +7959,22 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7987,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7977,7 +7997,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7997,34 +8017,34 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
+          <t>08:20采样：该车到重点站云山路灵山路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8038,7 +8058,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -8048,12 +8068,12 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -8073,12 +8093,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8091,24 +8111,24 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>07:35</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8121,24 +8141,24 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站五莲路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±10分钟</t>
+          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -8148,7 +8168,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8162,7 +8182,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8197,12 +8217,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8215,24 +8235,24 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8245,34 +8265,30 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站航津路地铁站 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8286,7 +8302,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8296,12 +8312,12 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8311,22 +8327,22 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8339,24 +8355,24 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>07:53</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8369,34 +8385,34 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路金桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±11分钟</t>
+          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±14分钟</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8410,7 +8426,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8445,12 +8461,12 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8479,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8473,7 +8489,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8493,34 +8509,34 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站航津路地铁站 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±12分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8534,7 +8550,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8549,7 +8565,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8569,12 +8585,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8587,24 +8603,24 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8617,19 +8633,19 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站同港路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站金高路行泰路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8639,12 +8655,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8658,7 +8674,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8693,12 +8709,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8727,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8721,7 +8737,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8741,34 +8757,34 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+          <t>08:20采样：该车到重点站金高路东靖路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8782,7 +8798,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8797,7 +8813,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8807,22 +8823,22 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8851,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8845,7 +8861,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8865,22 +8881,26 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站五莲路凌河路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8888,7 +8908,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8902,32 +8922,32 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8937,12 +8957,12 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8955,24 +8975,24 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8985,34 +9005,34 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±10分钟</t>
+          <t>08:10采样：该车到重点站航津路地铁站 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9026,7 +9046,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -9036,12 +9056,12 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -9051,22 +9071,22 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9099,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -9089,7 +9109,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -9109,34 +9129,34 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数102分钟估算，约±15分钟</t>
+          <t>08:20采样：该车到重点站花山路大同路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9150,7 +9170,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9160,12 +9180,12 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -9175,22 +9195,22 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9203,24 +9223,24 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9233,34 +9253,34 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+          <t>08:20采样：该车到重点站花山路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9274,7 +9294,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9284,12 +9304,12 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9299,22 +9319,22 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9327,24 +9347,24 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9357,34 +9377,34 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数113分钟估算，约±15分钟</t>
+          <t>08:20采样：该车到重点站五莲路凌河路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9398,47 +9418,787 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数102分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X77" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
+      <c r="AB77" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr">
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>113分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数113分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AD73" s="2" t="inlineStr">
-        <is>
-          <t>11/18</t>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-operations.xlsx
+++ b/data/export/2026-09-21-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2212,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3948,17 +3948,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6428,17 +6428,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8908,17 +8908,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10149,12 +10149,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10388,17 +10388,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
@@ -11676,27 +11676,31 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:23采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11704,7 +11708,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11728,12 +11732,12 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11753,7 +11757,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
@@ -11828,7 +11832,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11877,12 +11881,12 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11920,29 +11924,29 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>20:23采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -11952,7 +11956,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11976,12 +11980,12 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -12001,12 +12005,12 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12044,27 +12048,31 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:23采样，终点ETA 49分钟</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -12072,7 +12080,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12096,17 +12104,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12116,17 +12124,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -12164,24 +12172,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>20:23采样：该车到重点站博兴路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -12196,7 +12204,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12220,12 +12228,12 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -12245,12 +12253,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -12288,29 +12296,29 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -12320,7 +12328,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12344,12 +12352,12 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -12369,7 +12377,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12417,26 +12425,22 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:22采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12444,7 +12448,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12468,12 +12472,12 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12493,12 +12497,12 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -12541,19 +12545,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>22:27</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>21:22采样：该车到重点站长岛路台儿庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12568,7 +12572,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12597,7 +12601,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12612,17 +12616,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12820,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12865,12 +12869,12 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13312,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13357,12 +13361,12 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13486,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13606,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13800,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13840,17 +13844,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13920,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13965,7 +13969,7 @@
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>148.2</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
@@ -14040,7 +14044,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14089,7 +14093,7 @@
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
@@ -14288,7 +14292,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14408,7 +14412,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14457,7 +14461,7 @@
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
@@ -14532,7 +14536,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14581,12 +14585,12 @@
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14714,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -14776,7 +14780,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14825,12 +14829,12 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -14954,7 +14958,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15082,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -15144,7 +15148,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15193,12 +15197,12 @@
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -15322,7 +15326,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -15392,7 +15396,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15570,7 +15574,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15644,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15689,7 +15693,7 @@
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
@@ -15764,7 +15768,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15808,12 +15812,12 @@
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
@@ -16012,7 +16016,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16061,12 +16065,12 @@
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16574,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16644,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16689,12 +16693,12 @@
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -16942,7 +16946,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17012,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17052,17 +17056,17 @@
       </c>
       <c r="AB134" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC134" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -17132,7 +17136,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17181,7 +17185,7 @@
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>148.2</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
@@ -17380,7 +17384,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17429,7 +17433,7 @@
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
@@ -17504,7 +17508,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17628,7 +17632,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17677,7 +17681,7 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
@@ -17752,7 +17756,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17801,12 +17805,12 @@
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -17930,7 +17934,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -18054,7 +18058,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18128,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18173,12 +18177,12 @@
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -18302,7 +18306,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18376,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18550,7 +18554,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -18620,7 +18624,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18664,12 +18668,12 @@
       </c>
       <c r="AB147" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC147" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD147" s="2" t="inlineStr">
@@ -19170,7 +19174,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19240,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19426,7 +19430,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -19620,7 +19624,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19798,7 +19802,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -19868,7 +19872,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19917,7 +19921,7 @@
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
@@ -20042,7 +20046,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -20166,7 +20170,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20294,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -20414,7 +20418,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20906,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21030,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -21224,7 +21228,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21273,7 +21277,7 @@
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>148.2</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
@@ -21348,7 +21352,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21397,12 +21401,12 @@
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -21472,7 +21476,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21521,7 +21525,7 @@
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
@@ -21596,7 +21600,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21645,7 +21649,7 @@
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
@@ -21716,7 +21720,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21836,7 +21840,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21885,12 +21889,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -21960,7 +21964,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22084,7 +22088,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22208,7 +22212,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22257,12 +22261,12 @@
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -22328,7 +22332,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22377,12 +22381,12 @@
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -22448,7 +22452,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22492,12 +22496,12 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
@@ -22572,7 +22576,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22616,17 +22620,17 @@
       </c>
       <c r="AB179" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22878,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -22998,7 +23002,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23072,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23370,7 +23374,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -23618,7 +23622,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -23742,7 +23746,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -23866,7 +23870,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -23904,27 +23908,31 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 15分钟</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -23932,7 +23940,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23956,12 +23964,12 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
@@ -23981,12 +23989,12 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -24029,24 +24037,24 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N191" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O191" s="2" t="inlineStr">
@@ -24056,7 +24064,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24105,12 +24113,12 @@
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -24148,24 +24156,24 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数19分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N192" s="2" t="inlineStr">
@@ -24180,7 +24188,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24204,12 +24212,12 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
@@ -24229,7 +24237,7 @@
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
@@ -24272,29 +24280,29 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O193" s="2" t="inlineStr">
@@ -24304,7 +24312,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24328,12 +24336,12 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
@@ -24353,7 +24361,7 @@
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
@@ -24396,24 +24404,24 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路御桥路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
@@ -24428,7 +24436,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24452,12 +24460,12 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
@@ -24477,7 +24485,7 @@
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>148.2</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
@@ -24515,12 +24523,12 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -24548,7 +24556,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24556,10 +24564,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R195" s="2" t="inlineStr"/>
-      <c r="S195" s="2" t="inlineStr"/>
-      <c r="T195" s="2" t="inlineStr"/>
-      <c r="U195" s="2" t="inlineStr"/>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="U195" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V195" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24577,7 +24601,7 @@
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
@@ -24640,29 +24664,29 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±9分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O196" s="2" t="inlineStr">
@@ -24672,7 +24696,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24696,12 +24720,12 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
@@ -24721,12 +24745,12 @@
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -24764,29 +24788,29 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N197" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O197" s="2" t="inlineStr">
@@ -24796,7 +24820,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24820,12 +24844,12 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
@@ -24845,7 +24869,7 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
@@ -24883,36 +24907,32 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr"/>
       <c r="O198" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -24920,7 +24940,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24928,10 +24948,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R198" s="2" t="inlineStr"/>
-      <c r="S198" s="2" t="inlineStr"/>
-      <c r="T198" s="2" t="inlineStr"/>
-      <c r="U198" s="2" t="inlineStr"/>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="U198" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V198" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24944,17 +24980,17 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA198" s="2" t="inlineStr">
@@ -24964,12 +25000,12 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
@@ -25017,7 +25053,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -25029,12 +25065,12 @@
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±6分钟</t>
+          <t>20:41采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O199" s="2" t="inlineStr">
@@ -25044,7 +25080,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25141,19 +25177,19 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+          <t>21:21采样：该车到重点站五莲路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
@@ -25168,7 +25204,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25217,12 +25253,12 @@
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -25265,26 +25301,22 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 28分钟</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr"/>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -25292,7 +25324,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25316,12 +25348,12 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
@@ -25341,12 +25373,12 @@
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -25389,24 +25421,24 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±6分钟</t>
+          <t>21:21采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O202" s="2" t="inlineStr">
@@ -25416,7 +25448,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25465,12 +25497,12 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -25513,22 +25545,26 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N203" s="2" t="inlineStr"/>
+          <t>20:51采样：该车到重点站锦绣路罗山路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -25536,7 +25572,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25560,17 +25596,17 @@
       </c>
       <c r="X203" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y203" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z203" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA203" s="2" t="inlineStr">
@@ -25580,17 +25616,17 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -25645,12 +25681,12 @@
       <c r="L204" s="2" t="inlineStr"/>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±8分钟</t>
+          <t>21:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O204" s="2" t="inlineStr">
@@ -25660,7 +25696,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25689,7 +25725,7 @@
       </c>
       <c r="Y204" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z204" s="2" t="inlineStr">
@@ -25762,19 +25798,19 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+          <t>21:11采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O205" s="2" t="inlineStr">
@@ -25784,7 +25820,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25813,7 +25849,7 @@
       </c>
       <c r="Y205" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z205" s="2" t="inlineStr">
@@ -25833,12 +25869,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -25904,7 +25940,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25965,12 +26001,12 @@
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26250,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26338,7 +26374,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -26408,7 +26444,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26457,12 +26493,12 @@
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26532,7 +26568,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26581,7 +26617,7 @@
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
@@ -26710,7 +26746,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -26830,7 +26866,7 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -26900,7 +26936,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26949,7 +26985,7 @@
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
@@ -27024,7 +27060,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27068,17 +27104,17 @@
       </c>
       <c r="AB215" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC215" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -27202,7 +27238,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27326,7 +27362,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -27764,7 +27800,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27813,12 +27849,12 @@
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -28062,7 +28098,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28310,7 +28346,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -28380,7 +28416,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28429,7 +28465,7 @@
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
@@ -28558,7 +28594,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28718,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -28748,7 +28784,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28797,12 +28833,12 @@
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28926,7 +28962,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28996,7 +29032,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29040,17 +29076,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -29120,7 +29156,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29169,7 +29205,7 @@
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
@@ -29422,7 +29458,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29542,7 +29578,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -29736,7 +29772,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29785,12 +29821,12 @@
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30070,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -30100,7 +30136,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30161,7 +30197,7 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
@@ -30290,7 +30326,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30450,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -30480,7 +30516,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30536,17 +30572,17 @@
       </c>
       <c r="AB243" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -30666,7 +30702,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -30914,7 +30950,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -31158,7 +31194,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -31406,7 +31442,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31530,7 +31566,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -31654,7 +31690,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -31778,7 +31814,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -32022,7 +32058,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -32270,7 +32306,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -32518,7 +32554,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32642,7 +32678,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -32712,7 +32748,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32761,12 +32797,12 @@
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -32890,7 +32926,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -33014,7 +33050,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33262,7 +33298,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33332,7 +33368,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33381,12 +33417,12 @@
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -33576,7 +33612,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33625,7 +33661,7 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -33994,7 +34030,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -34064,7 +34100,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34113,7 +34149,7 @@
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
@@ -34188,7 +34224,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34237,12 +34273,12 @@
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -34490,7 +34526,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -34560,7 +34596,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34604,17 +34640,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -34738,7 +34774,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -34862,7 +34898,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -34932,7 +34968,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34981,12 +35017,12 @@
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -35234,7 +35270,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -35482,7 +35518,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35552,7 +35588,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35601,12 +35637,12 @@
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35800,7 +35836,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35849,7 +35885,7 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
@@ -36098,7 +36134,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -36168,7 +36204,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36217,7 +36253,7 @@
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36288,7 +36324,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36337,12 +36373,12 @@
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -36466,7 +36502,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -36714,7 +36750,7 @@
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -36784,7 +36820,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36828,17 +36864,17 @@
       </c>
       <c r="AB294" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -36958,7 +36994,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -37152,7 +37188,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37201,12 +37237,12 @@
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -37454,7 +37490,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37648,7 +37684,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37697,12 +37733,12 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37745,12 +37781,12 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
@@ -37772,7 +37808,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37821,7 +37857,7 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
@@ -37896,7 +37932,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37945,7 +37981,7 @@
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
@@ -37988,27 +38024,31 @@
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -38016,7 +38056,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38040,17 +38080,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -38060,17 +38100,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -38108,29 +38148,29 @@
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车21:40，减去该车自身同类时段历史终点停站中位数32分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N305" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O305" s="2" t="inlineStr">
@@ -38140,7 +38180,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38164,12 +38204,12 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
@@ -38189,12 +38229,12 @@
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -38232,29 +38272,29 @@
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N306" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O306" s="2" t="inlineStr">
@@ -38264,7 +38304,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38288,12 +38328,12 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
@@ -38313,12 +38353,12 @@
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -38356,29 +38396,29 @@
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr"/>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N307" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O307" s="2" t="inlineStr">
@@ -38388,7 +38428,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38412,12 +38452,12 @@
       </c>
       <c r="X307" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y307" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z307" s="2" t="inlineStr">
@@ -38437,12 +38477,12 @@
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -38485,24 +38525,24 @@
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="2" t="inlineStr"/>
       <c r="M308" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N308" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O308" s="2" t="inlineStr">
@@ -38512,7 +38552,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38541,7 +38581,7 @@
       </c>
       <c r="Y308" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z308" s="2" t="inlineStr">
@@ -38561,7 +38601,7 @@
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
@@ -38636,7 +38676,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q309" s="2" t="inlineStr">
@@ -38685,12 +38725,12 @@
       </c>
       <c r="AC309" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD309" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
